--- a/mode_docx_gen/pmi_tokz/part/lvtoc/ptoc1/PTOC1.xlsx
+++ b/mode_docx_gen/pmi_tokz/part/lvtoc/ptoc1/PTOC1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.11.240\Company\Ivanovo\Документация ЮНИТ М300\Разработка\Схемы ФБ ЮНИТ-М3\Трансформатор\ИЭУ Т 35 кВ Россети\01. Разработка ФБ\29. ТО 35\_xlsx\funcs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\www5\mode_docx_gen\pmi_tokz\part\lvtoc\ptoc1\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505"/>
   </bookViews>
   <sheets>
     <sheet name="Signals" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="101">
   <si>
     <t>Parameter</t>
   </si>
@@ -317,13 +317,19 @@
   </si>
   <si>
     <t>Токовая отсечка</t>
+  </si>
+  <si>
+    <t>alias</t>
+  </si>
+  <si>
+    <t>Iset</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -343,6 +349,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="5">
@@ -369,7 +382,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -392,11 +405,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -434,6 +469,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -741,7 +782,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:AE12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -760,7 +801,7 @@
     <col min="29" max="30" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -851,8 +892,11 @@
       <c r="AD1" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="AE1" s="15" t="s">
+        <v>99</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>36</v>
       </c>
@@ -944,7 +988,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>36</v>
       </c>
@@ -1036,7 +1080,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>36</v>
       </c>
@@ -1128,7 +1172,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>36</v>
       </c>
@@ -1220,7 +1264,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>36</v>
       </c>
@@ -1312,7 +1356,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>36</v>
       </c>
@@ -1404,7 +1448,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>36</v>
       </c>
@@ -1496,7 +1540,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>68</v>
       </c>
@@ -1588,7 +1632,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>68</v>
       </c>
@@ -1680,7 +1724,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>68</v>
       </c>
@@ -1771,8 +1815,11 @@
       <c r="AD11" s="8" t="s">
         <v>39</v>
       </c>
+      <c r="AE11" s="16" t="s">
+        <v>100</v>
+      </c>
     </row>
-    <row r="12" spans="1:30" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>68</v>
       </c>
@@ -1862,6 +1909,9 @@
       </c>
       <c r="AD12" s="8" t="s">
         <v>39</v>
+      </c>
+      <c r="AE12" s="16" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
